--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260609.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260609.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>157,415</t>
+          <t>158,315</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.33%</t>
+          <t>27.40%</t>
         </is>
       </c>
     </row>
@@ -633,56 +633,56 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>114,250</t>
+          <t>114,700</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.59%</t>
+          <t>10.42%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MRVL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Marvell Technology Inc</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>58,105</t>
+          <t>18,055</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.34%</t>
+          <t>7.33%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>MRVL US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>Marvell Technology Inc</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>17,955</t>
+          <t>58,455</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.34%</t>
+          <t>6.89%</t>
         </is>
       </c>
     </row>
@@ -699,56 +699,56 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>138,595</t>
+          <t>139,095</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.09%</t>
+          <t>5.21%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>67,920</t>
+          <t>8,538,019</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.77%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>6,535</t>
+          <t>68,220</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
@@ -765,122 +765,122 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>74,715</t>
+          <t>74,815</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>51,605</t>
+          <t>6,535</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>22,535</t>
+          <t>51,705</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>20,873</t>
+          <t>22,635</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>36,020</t>
+          <t>20,973</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>87,915</t>
+          <t>36,120</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
@@ -897,34 +897,34 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>23,175</t>
+          <t>23,275</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>125,391,714</t>
+          <t>88,415</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>58,425</t>
+          <t>58,575</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>30,378</t>
+          <t>30,478</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>22,290</t>
+          <t>22,390</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>41,400</t>
+          <t>41,500</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>67,908</t>
+          <t>68,008</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>13,361</t>
+          <t>13,461</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>24,408</t>
+          <t>24,508</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1122,51 +1122,51 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>145,045</t>
+          <t>21,215</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>21,115</t>
+          <t>145,195</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1183,19 +1183,19 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>22,547</t>
+          <t>22,647</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>2,264,380</t>
+          <t>68,587,890</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>18,211</t>
+          <t>18,311</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>42,940</t>
+          <t>43,040</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>49,370</t>
+          <t>49,520</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>13,465</t>
+          <t>13,615</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>6,235,615</t>
+          <t>-470,610</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
